--- a/companies/tlb/model.xlsx
+++ b/companies/tlb/model.xlsx
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4b1328f5f197cab7</t>
+          <t>aea60d7d03834c05</t>
         </is>
       </c>
     </row>

--- a/companies/tlb/model.xlsx
+++ b/companies/tlb/model.xlsx
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>aea60d7d03834c05</t>
+          <t>813f5594bba51005</t>
         </is>
       </c>
     </row>

--- a/companies/tlb/model.xlsx
+++ b/companies/tlb/model.xlsx
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>813f5594bba51005</t>
+          <t>1786049a6c671537</t>
         </is>
       </c>
     </row>

--- a/companies/tlb/model.xlsx
+++ b/companies/tlb/model.xlsx
@@ -3711,7 +3711,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1786049a6c671537</t>
+          <t>daa847eeeff1695c</t>
         </is>
       </c>
     </row>

--- a/companies/tlb/model.xlsx
+++ b/companies/tlb/model.xlsx
@@ -115,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -158,11 +158,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="5"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="6"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="7"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -183,6 +186,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="7"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -845,7 +851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1057,33 +1063,29 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>감가상각비 실적</t>
+          <t>순이익 실적 마스크</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>dep_actual</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>억원</t>
-        </is>
-      </c>
+          <t>ni_hist</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="9" t="n">
-        <v>35.71458</v>
+        <v>1</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>45.83276</v>
+        <v>1</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>53.90911</v>
+        <v>1</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>59.76686</v>
+        <v>1</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>75.01629</v>
+        <v>1</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>0</v>
@@ -1102,71 +1104,71 @@
       </c>
       <c r="N6" s="11" t="inlineStr">
         <is>
-          <t>[객관] 네 개 사업보고서의 당기/전기가 연쇄적으로 일치해 교차검증됐다.</t>
+          <t>[객관] 실적 연도 표시(1). 순이익은 적자 연도가 있어 "실적 &gt; 0" 관용구를 쓸 수 없다 — LGD·삼성전자 DS에서 확립한 hist 마스크 패턴.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>감가상각 증가율</t>
+          <t>순이익 실적</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>dep_g</t>
+          <t>ni_actual</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="13" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="J7" s="13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K7" s="13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="L7" s="13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M7" s="13" t="n">
-        <v>0.08</v>
+          <t>억원</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>124.11147392</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>305.556354</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>25.14693255</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>36.17832158</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>190.49050674</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>[주관] 2025년 CAPEX가 368.8억으로 감가상각비(75.0억)의 **4.9배**다. 증설이 진행 중이라는 뜻이고, 그 투자분이 2026~2027년에 상각으로 들어온다. 실적 4년 연평균 +20.4%에서 2026년을 +35%로 올린 근거가 이것이다. 생산능력 가정과 방향이 일치해야 한다 — 능력을 늘리면서 상각이 늘지 않는 모델은 성립하지 않는다.</t>
+          <t>[객관] 연결 지배주주 순이익 확정값 (사업보고서 연결포괄손익계산서).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>기타비용 실적</t>
+          <t>영업외손익</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>other_actual</t>
+          <t>nonop</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1175,19 +1177,19 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>1611.4808117</v>
+        <v>15.00632322</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>1785.00435726</v>
+        <v>-2.30913692</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>1628.70819668</v>
+        <v>2.21248076</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>1706.66660828</v>
+        <v>15.43167313</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>2250.33474673</v>
+        <v>-15.8505192</v>
       </c>
       <c r="I8" s="10" t="n">
         <v>0</v>
@@ -1206,19 +1208,19 @@
       </c>
       <c r="N8" s="11" t="inlineStr">
         <is>
-          <t>[객관] 확정값에서 역산. 세 항목 모두 공시값이라 결과도 확정이다.</t>
+          <t>[주관 추정 · 실적은 공시값] 영업외손익 = 세전이익 − 영업이익. 실적 +15/−2/+2/+15/−16억 등락 — 규모가 작아 0 고정.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>기타비용률</t>
+          <t>실효세율</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>other_ratio</t>
+          <t>tax_rate</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1242,229 +1244,645 @@
         <v>0</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>0.83</v>
+        <v>0.22</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>0.825</v>
+        <v>0.22</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>0.82</v>
+        <v>0.22</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.22</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>[주관] 매출 대비 기타비용. 실적 90.5 → 80.6 → 95.1 → 94.8 → 87.1%로 **사이클에 따라 15%p나 흔들린다** — 고정비 비중이 높은 장치산업의 특징이다. 2026 상반기 실적(매출 1,640.8억 · 영업이익 234.9억)에서 역산하면 82.9% 수준이라 2026년을 83.0%로 두고 연 0.5%p씩만 개선한다고 봤다. 2022년 저점(80.6%)까지 가는 것은 Bull에서만 가정한다.</t>
+          <t>[주관] 실효세율. 실적 16.6/20.1/23.2/26.6/22.3% — 22%.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>생산능력</t>
+          <t>지배지분 비율</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>capacity</t>
+          <t>ctrl_ratio</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>천㎡</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>342</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>348</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>348</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>348</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>348</v>
-      </c>
-      <c r="I10" s="10" t="n">
-        <v>360</v>
-      </c>
-      <c r="J10" s="10" t="n">
-        <v>400</v>
-      </c>
-      <c r="K10" s="10" t="n">
-        <v>430</v>
-      </c>
-      <c r="L10" s="10" t="n">
-        <v>450</v>
-      </c>
-      <c r="M10" s="10" t="n">
-        <v>460</v>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>[객관 실적 / 주관 추정] 공시 기준 월 29,000㎡ × 12개월 = 348천㎡로 2022년 이후 **4년째 고정**이다. 이것이 이 모델의 상한선이고, 증설 없이는 물량이 348천㎡를 넘을 수 없다. 추정 구간은 2025년 CAPEX 368.8억(감가상각의 4.9배)을 근거로 늘렸으나 **회사가 증설 계획을 수치로 공시하지 않아 이 부분은 판단이다**. 민감도 뷰에서 영향도를 확인할 것.</t>
+          <t>[주관] 지배지분 비율. 비지배 몫이 미미(음수) — 100%.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>가동률</t>
+          <t>상장주식수</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>util</t>
+          <t>shares</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>0.860946317519296</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>0.8028427797711249</v>
-      </c>
-      <c r="F11" s="12" t="n">
-        <v>0.6552676032886309</v>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>0.613460265575915</v>
-      </c>
-      <c r="H11" s="12" t="n">
-        <v>0.6780144209429898</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="K11" s="13" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="L11" s="13" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>0.78</v>
+          <t>백만주</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>23.70126</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>23.70126</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>23.70126</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>23.70126</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>23.70126</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>23.70126</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>23.70126</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>23.70126</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>23.70126</v>
+      </c>
+      <c r="M11" s="10" t="n">
+        <v>23.70126</v>
       </c>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>[객관 실적 / 주관 추정] 출하량 ÷ 생산능력. 실적 86.1 → 80.3 → 65.5 → 61.3 → 67.8%. 공시의 가동률(생산실적 기준)과는 재고 변동만큼 다르다. 2026 상반기 실적에서 역산한 연환산 가동률이 69.3%라 2026년을 70.0%로 두고 연 2%p씩 올렸다. **2021년 수준(86.1%) 복귀는 가정하지 않았다** — 그 회복이 이 종목의 가장 큰 상방이고 Bull에서만 반영한다.</t>
+          <t>[객관] 상장주식수 23,701,260주(2026 무상증자 후) 고정. **공시 EPS·DPS는 증자 전 주식수 기준**이라 실적 연도의 주당 값과 기준이 다르다 — 현재가와 비교하는 용도로는 현재 주식수가 맞다.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>단가</t>
+          <t>DPS 실적</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>dps_a</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>억원/천㎡</t>
+          <t>원</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>6.04869</v>
+        <v>250</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>7.92973</v>
+        <v>300</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>7.51236</v>
+        <v>200</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>8.4316</v>
+        <v>200</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>10.95566</v>
+        <v>450</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>13.42</v>
+        <v>0</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>14.23</v>
+        <v>0</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>14.66</v>
+        <v>0</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>14.95</v>
+        <v>0</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>15.25</v>
+        <v>0</v>
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>[객관 실적 / 주관 추정] 공시 "주요제품 가격변동 추이"(원/㎡)를 억원/천㎡로 환산. 실적 604,869 → 792,973 → 751,236 → 843,160 → 1,095,566원/㎡. 2026 상반기 공시값이 **1,361,056원/㎡로 +24.2%** 더 올랐다. 하반기 소폭 조정을 가정해 2026년 연평균을 13.42(=1,342,000원/㎡)로 두고, 이후 +6/+3/+2/+2%로 체감시켰다. 단가 상승은 DDR5·고다층 전환의 결과이므로 전환이 끝나면 멈춘다 — 영구히 오르는 값이 아니다.</t>
+          <t>[객관] 주당 현금배당(당시 주식수 기준). 실적 250/300/200/200/450원.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
+          <t>배당성향</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>payout</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>[주관] 배당성향. 실적 9.9/9.7/77.9/53.8/23.0% — 이익 정상 연도 기준 **23%**.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>감가상각비 실적</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>dep_actual</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>35.71458</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>45.83276</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>53.90911</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>59.76686</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>75.01629</v>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>[객관] 네 개 사업보고서의 당기/전기가 연쇄적으로 일치해 교차검증됐다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>감가상각 증가율</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>dep_g</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>[주관] 2025년 CAPEX가 368.8억으로 감가상각비(75.0억)의 **4.9배**다. 증설이 진행 중이라는 뜻이고, 그 투자분이 2026~2027년에 상각으로 들어온다. 실적 4년 연평균 +20.4%에서 2026년을 +35%로 올린 근거가 이것이다. 생산능력 가정과 방향이 일치해야 한다 — 능력을 늘리면서 상각이 늘지 않는 모델은 성립하지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>기타비용 실적</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>other_actual</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>1611.4808117</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>1785.00435726</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>1628.70819668</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>1706.66660828</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>2250.33474673</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>[객관] 확정값에서 역산. 세 항목 모두 공시값이라 결과도 확정이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>기타비용률</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>other_ratio</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>[주관] 매출 대비 기타비용. 실적 90.5 → 80.6 → 95.1 → 94.8 → 87.1%로 **사이클에 따라 15%p나 흔들린다** — 고정비 비중이 높은 장치산업의 특징이다. 2026 상반기 실적(매출 1,640.8억 · 영업이익 234.9억)에서 역산하면 82.9% 수준이라 2026년을 83.0%로 두고 연 0.5%p씩만 개선한다고 봤다. 2022년 저점(80.6%)까지 가는 것은 Bull에서만 가정한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>생산능력</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>천㎡</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>342</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>348</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>348</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>348</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>348</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>360</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="K18" s="10" t="n">
+        <v>430</v>
+      </c>
+      <c r="L18" s="10" t="n">
+        <v>450</v>
+      </c>
+      <c r="M18" s="10" t="n">
+        <v>460</v>
+      </c>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>[객관 실적 / 주관 추정] 공시 기준 월 29,000㎡ × 12개월 = 348천㎡로 2022년 이후 **4년째 고정**이다. 이것이 이 모델의 상한선이고, 증설 없이는 물량이 348천㎡를 넘을 수 없다. 추정 구간은 2025년 CAPEX 368.8억(감가상각의 4.9배)을 근거로 늘렸으나 **회사가 증설 계획을 수치로 공시하지 않아 이 부분은 판단이다**. 민감도 뷰에서 영향도를 확인할 것.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>가동률</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>util</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>0.860946317519296</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>0.8028427797711249</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>0.6552676032886309</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>0.613460265575915</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>0.6780144209429898</v>
+      </c>
+      <c r="I19" s="13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>[객관 실적 / 주관 추정] 출하량 ÷ 생산능력. 실적 86.1 → 80.3 → 65.5 → 61.3 → 67.8%. 공시의 가동률(생산실적 기준)과는 재고 변동만큼 다르다. 2026 상반기 실적에서 역산한 연환산 가동률이 69.3%라 2026년을 70.0%로 두고 연 2%p씩 올렸다. **2021년 수준(86.1%) 복귀는 가정하지 않았다** — 그 회복이 이 종목의 가장 큰 상방이고 Bull에서만 반영한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>단가</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>억원/천㎡</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>6.04869</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>7.92973</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>7.51236</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>8.4316</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>10.95566</v>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="K20" s="10" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="L20" s="10" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="M20" s="10" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="N20" s="11" t="inlineStr">
+        <is>
+          <t>[객관 실적 / 주관 추정] 공시 "주요제품 가격변동 추이"(원/㎡)를 억원/천㎡로 환산. 실적 604,869 → 792,973 → 751,236 → 843,160 → 1,095,566원/㎡. 2026 상반기 공시값이 **1,361,056원/㎡로 +24.2%** 더 올랐다. 하반기 소폭 조정을 가정해 2026년 연평균을 13.42(=1,342,000원/㎡)로 두고, 이후 +6/+3/+2/+2%로 체감시켰다. 단가 상승은 DDR5·고다층 전환의 결과이므로 전환이 끝나면 멈춘다 — 영구히 오르는 값이 아니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
           <t>순차입금</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>net_debt</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>억원</t>
         </is>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D21" s="9" t="n">
         <v>70.03945403</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E21" s="9" t="n">
         <v>-52.71277978</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F21" s="9" t="n">
         <v>298.34463868</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G21" s="9" t="n">
         <v>334.64758095</v>
       </c>
-      <c r="H13" s="9" t="n">
+      <c r="H21" s="9" t="n">
         <v>617.63877813</v>
       </c>
-      <c r="I13" s="10" t="n">
+      <c r="I21" s="10" t="n">
         <v>617.63877813</v>
       </c>
-      <c r="J13" s="10" t="n">
+      <c r="J21" s="10" t="n">
         <v>617.63877813</v>
       </c>
-      <c r="K13" s="10" t="n">
+      <c r="K21" s="10" t="n">
         <v>617.63877813</v>
       </c>
-      <c r="L13" s="10" t="n">
+      <c r="L21" s="10" t="n">
         <v>617.63877813</v>
       </c>
-      <c r="M13" s="10" t="n">
+      <c r="M21" s="10" t="n">
         <v>617.63877813</v>
       </c>
-      <c r="N13" s="11" t="inlineStr">
+      <c r="N21" s="11" t="inlineStr">
         <is>
           <t>[객관 실적 / 추정 구간 고정] 차입금(단기+유동성장기+장기) − 현금및현금성자산. 리스부채 제외. 2022년 −52.7억(순현금)에서 2025년 617.6억으로 3년 만에 670억이 늘었다 — 증설 투자를 차입으로 감당한 결과다. 시가총액의 6.3%로 삼성전기·KT&amp;G보다 밸류에이션 민감도가 크다. 추정 구간은 2025년 수준으로 고정했으나, CAPEX가 감가상각의 5배인 국면이라 실제로는 더 늘 가능성이 높다.</t>
         </is>
@@ -1481,7 +1899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1649,43 +2067,43 @@
         </is>
       </c>
       <c r="D5" s="14">
-        <f>(D6-D22)</f>
+        <f>(D6-D33)</f>
         <v/>
       </c>
       <c r="E5" s="14">
-        <f>(E6-E22)</f>
+        <f>(E6-E33)</f>
         <v/>
       </c>
       <c r="F5" s="14">
-        <f>(F6-F22)</f>
+        <f>(F6-F33)</f>
         <v/>
       </c>
       <c r="G5" s="14">
-        <f>(G6-G22)</f>
+        <f>(G6-G33)</f>
         <v/>
       </c>
       <c r="H5" s="14">
-        <f>(H6-H22)</f>
+        <f>(H6-H33)</f>
         <v/>
       </c>
       <c r="I5" s="14">
-        <f>(I6-I22)</f>
+        <f>(I6-I33)</f>
         <v/>
       </c>
       <c r="J5" s="14">
-        <f>(J6-J22)</f>
+        <f>(J6-J33)</f>
         <v/>
       </c>
       <c r="K5" s="14">
-        <f>(K6-K22)</f>
+        <f>(K6-K33)</f>
         <v/>
       </c>
       <c r="L5" s="14">
-        <f>(L6-L22)</f>
+        <f>(L6-L33)</f>
         <v/>
       </c>
       <c r="M5" s="14">
-        <f>(M6-M22)</f>
+        <f>(M6-M33)</f>
         <v/>
       </c>
     </row>
@@ -1810,43 +2228,43 @@
         </is>
       </c>
       <c r="D8" s="16">
-        <f>(D9+D11)</f>
+        <f>(D9+D22)</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>(E9+E11)</f>
+        <f>(E9+E22)</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>(F9+F11)</f>
+        <f>(F9+F22)</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>(G9+G11)</f>
+        <f>(G9+G22)</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>(H9+H11)</f>
+        <f>(H9+H22)</f>
         <v/>
       </c>
       <c r="I8" s="17">
-        <f>(I9+I11)</f>
+        <f>(I9+I22)</f>
         <v/>
       </c>
       <c r="J8" s="17">
-        <f>(J9+J11)</f>
+        <f>(J9+J22)</f>
         <v/>
       </c>
       <c r="K8" s="17">
-        <f>(K9+K11)</f>
+        <f>(K9+K22)</f>
         <v/>
       </c>
       <c r="L8" s="17">
-        <f>(L9+L11)</f>
+        <f>(L9+L22)</f>
         <v/>
       </c>
       <c r="M8" s="17">
-        <f>(M9+M11)</f>
+        <f>(M9+M22)</f>
         <v/>
       </c>
     </row>
@@ -1867,55 +2285,55 @@
         </is>
       </c>
       <c r="D9" s="16">
-        <f>(D17-D10)</f>
+        <f>(D28-D21)</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>(E17-E10)</f>
+        <f>(E28-E21)</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>(F17-F10)</f>
+        <f>(F28-F21)</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>(G17-G10)</f>
+        <f>(G28-G21)</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>(H17-H10)</f>
+        <f>(H28-H21)</f>
         <v/>
       </c>
       <c r="I9" s="17">
-        <f>(I17-I10)</f>
+        <f>(I28-I21)</f>
         <v/>
       </c>
       <c r="J9" s="17">
-        <f>(J17-J10)</f>
+        <f>(J28-J21)</f>
         <v/>
       </c>
       <c r="K9" s="17">
-        <f>(K17-K10)</f>
+        <f>(K28-K21)</f>
         <v/>
       </c>
       <c r="L9" s="17">
-        <f>(L17-L10)</f>
+        <f>(L28-L21)</f>
         <v/>
       </c>
       <c r="M9" s="17">
-        <f>(M17-M10)</f>
+        <f>(M28-M21)</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>총비용</t>
+          <t>지배주주 순이익 (참고)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>total_cost</t>
+          <t>net_income</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1924,647 +2342,1190 @@
         </is>
       </c>
       <c r="D10" s="16">
-        <f>(D11+D14)</f>
+        <f>IF((D11&gt;0),D12,(((D9+D13)*(1-D14))*D15))</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>(E11+E14)</f>
+        <f>IF((E11&gt;0),E12,(((E9+E13)*(1-E14))*E15))</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>(F11+F14)</f>
+        <f>IF((F11&gt;0),F12,(((F9+F13)*(1-F14))*F15))</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>(G11+G14)</f>
+        <f>IF((G11&gt;0),G12,(((G9+G13)*(1-G14))*G15))</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>(H11+H14)</f>
+        <f>IF((H11&gt;0),H12,(((H9+H13)*(1-H14))*H15))</f>
         <v/>
       </c>
       <c r="I10" s="17">
-        <f>(I11+I14)</f>
+        <f>IF((I11&gt;0),I12,(((I9+I13)*(1-I14))*I15))</f>
         <v/>
       </c>
       <c r="J10" s="17">
-        <f>(J11+J14)</f>
+        <f>IF((J11&gt;0),J12,(((J9+J13)*(1-J14))*J15))</f>
         <v/>
       </c>
       <c r="K10" s="17">
-        <f>(K11+K14)</f>
+        <f>IF((K11&gt;0),K12,(((K9+K13)*(1-K14))*K15))</f>
         <v/>
       </c>
       <c r="L10" s="17">
-        <f>(L11+L14)</f>
+        <f>IF((L11&gt;0),L12,(((L9+L13)*(1-L14))*L15))</f>
         <v/>
       </c>
       <c r="M10" s="17">
-        <f>(M11+M14)</f>
+        <f>IF((M11&gt;0),M12,(((M9+M13)*(1-M14))*M15))</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>감가상각비</t>
+          <t>순이익 실적 마스크</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>dep_total</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+          <t>ni_hist</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>순이익 실적</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ni_actual</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>억원</t>
         </is>
       </c>
-      <c r="D11" s="16">
-        <f>IF((D12&gt;0),D12,(0*(1+D13)))</f>
-        <v/>
-      </c>
-      <c r="E11" s="16">
-        <f>IF((E12&gt;0),E12,(D11*(1+E13)))</f>
-        <v/>
-      </c>
-      <c r="F11" s="16">
-        <f>IF((F12&gt;0),F12,(E11*(1+F13)))</f>
-        <v/>
-      </c>
-      <c r="G11" s="16">
-        <f>IF((G12&gt;0),G12,(F11*(1+G13)))</f>
-        <v/>
-      </c>
-      <c r="H11" s="16">
-        <f>IF((H12&gt;0),H12,(G11*(1+H13)))</f>
-        <v/>
-      </c>
-      <c r="I11" s="17">
-        <f>IF((I12&gt;0),I12,(H11*(1+I13)))</f>
-        <v/>
-      </c>
-      <c r="J11" s="17">
-        <f>IF((J12&gt;0),J12,(I11*(1+J13)))</f>
-        <v/>
-      </c>
-      <c r="K11" s="17">
-        <f>IF((K12&gt;0),K12,(J11*(1+K13)))</f>
-        <v/>
-      </c>
-      <c r="L11" s="17">
-        <f>IF((L12&gt;0),L12,(K11*(1+L13)))</f>
-        <v/>
-      </c>
-      <c r="M11" s="17">
-        <f>IF((M12&gt;0),M12,(L11*(1+M13)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>감가상각비 실적</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>dep_actual</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="D12" s="19" t="n">
+        <v>124.11147392</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>305.556354</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>25.14693255</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>36.17832158</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>190.49050674</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>영업외손익</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>nonop</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>억원</t>
         </is>
       </c>
-      <c r="D12" s="19" t="n">
-        <v>35.71458</v>
-      </c>
-      <c r="E12" s="19" t="n">
-        <v>45.83276</v>
-      </c>
-      <c r="F12" s="19" t="n">
-        <v>53.90911</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <v>59.76686</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <v>75.01629</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>감가상각 증가율</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>dep_g</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="26" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="J13" s="26" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K13" s="26" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="L13" s="26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M13" s="26" t="n">
-        <v>0.08</v>
+      <c r="D13" s="19" t="n">
+        <v>15.00632322</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>-2.30913692</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>2.21248076</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>15.43167313</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>-15.8505192</v>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="23" t="inlineStr">
         <is>
+          <t>실효세율</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="25" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J14" s="25" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K14" s="25" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L14" s="25" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="M14" s="25" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>지배지분 비율</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>ctrl_ratio</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>EPS (참고)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="D16" s="16">
+        <f>((D10/D17)*100)</f>
+        <v/>
+      </c>
+      <c r="E16" s="16">
+        <f>((E10/E17)*100)</f>
+        <v/>
+      </c>
+      <c r="F16" s="16">
+        <f>((F10/F17)*100)</f>
+        <v/>
+      </c>
+      <c r="G16" s="16">
+        <f>((G10/G17)*100)</f>
+        <v/>
+      </c>
+      <c r="H16" s="16">
+        <f>((H10/H17)*100)</f>
+        <v/>
+      </c>
+      <c r="I16" s="17">
+        <f>((I10/I17)*100)</f>
+        <v/>
+      </c>
+      <c r="J16" s="17">
+        <f>((J10/J17)*100)</f>
+        <v/>
+      </c>
+      <c r="K16" s="17">
+        <f>((K10/K17)*100)</f>
+        <v/>
+      </c>
+      <c r="L16" s="17">
+        <f>((L10/L17)*100)</f>
+        <v/>
+      </c>
+      <c r="M16" s="17">
+        <f>((M10/M17)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>상장주식수</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>shares</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>백만주</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>23.70126</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>23.70126</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>23.70126</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>23.70126</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>23.70126</v>
+      </c>
+      <c r="I17" s="20" t="n">
+        <v>23.70126</v>
+      </c>
+      <c r="J17" s="20" t="n">
+        <v>23.70126</v>
+      </c>
+      <c r="K17" s="20" t="n">
+        <v>23.70126</v>
+      </c>
+      <c r="L17" s="20" t="n">
+        <v>23.70126</v>
+      </c>
+      <c r="M17" s="20" t="n">
+        <v>23.70126</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>DPS (참고)</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="D18" s="16">
+        <f>IF((D11&gt;0),D19,(D16*D20))</f>
+        <v/>
+      </c>
+      <c r="E18" s="16">
+        <f>IF((E11&gt;0),E19,(E16*E20))</f>
+        <v/>
+      </c>
+      <c r="F18" s="16">
+        <f>IF((F11&gt;0),F19,(F16*F20))</f>
+        <v/>
+      </c>
+      <c r="G18" s="16">
+        <f>IF((G11&gt;0),G19,(G16*G20))</f>
+        <v/>
+      </c>
+      <c r="H18" s="16">
+        <f>IF((H11&gt;0),H19,(H16*H20))</f>
+        <v/>
+      </c>
+      <c r="I18" s="17">
+        <f>IF((I11&gt;0),I19,(I16*I20))</f>
+        <v/>
+      </c>
+      <c r="J18" s="17">
+        <f>IF((J11&gt;0),J19,(J16*J20))</f>
+        <v/>
+      </c>
+      <c r="K18" s="17">
+        <f>IF((K11&gt;0),K19,(K16*K20))</f>
+        <v/>
+      </c>
+      <c r="L18" s="17">
+        <f>IF((L11&gt;0),L19,(L16*L20))</f>
+        <v/>
+      </c>
+      <c r="M18" s="17">
+        <f>IF((M11&gt;0),M19,(M16*M20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>DPS 실적</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>dps_a</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>250</v>
+      </c>
+      <c r="E19" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="F19" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>450</v>
+      </c>
+      <c r="I19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>배당성향</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>payout</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="25" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J20" s="25" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K20" s="25" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L20" s="25" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M20" s="25" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>총비용</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>total_cost</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+      <c r="D21" s="16">
+        <f>(D22+D25)</f>
+        <v/>
+      </c>
+      <c r="E21" s="16">
+        <f>(E22+E25)</f>
+        <v/>
+      </c>
+      <c r="F21" s="16">
+        <f>(F22+F25)</f>
+        <v/>
+      </c>
+      <c r="G21" s="16">
+        <f>(G22+G25)</f>
+        <v/>
+      </c>
+      <c r="H21" s="16">
+        <f>(H22+H25)</f>
+        <v/>
+      </c>
+      <c r="I21" s="17">
+        <f>(I22+I25)</f>
+        <v/>
+      </c>
+      <c r="J21" s="17">
+        <f>(J22+J25)</f>
+        <v/>
+      </c>
+      <c r="K21" s="17">
+        <f>(K22+K25)</f>
+        <v/>
+      </c>
+      <c r="L21" s="17">
+        <f>(L22+L25)</f>
+        <v/>
+      </c>
+      <c r="M21" s="17">
+        <f>(M22+M25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>dep_total</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+      <c r="D22" s="16">
+        <f>IF((D23&gt;0),D23,(0*(1+D24)))</f>
+        <v/>
+      </c>
+      <c r="E22" s="16">
+        <f>IF((E23&gt;0),E23,(D22*(1+E24)))</f>
+        <v/>
+      </c>
+      <c r="F22" s="16">
+        <f>IF((F23&gt;0),F23,(E22*(1+F24)))</f>
+        <v/>
+      </c>
+      <c r="G22" s="16">
+        <f>IF((G23&gt;0),G23,(F22*(1+G24)))</f>
+        <v/>
+      </c>
+      <c r="H22" s="16">
+        <f>IF((H23&gt;0),H23,(G22*(1+H24)))</f>
+        <v/>
+      </c>
+      <c r="I22" s="17">
+        <f>IF((I23&gt;0),I23,(H22*(1+I24)))</f>
+        <v/>
+      </c>
+      <c r="J22" s="17">
+        <f>IF((J23&gt;0),J23,(I22*(1+J24)))</f>
+        <v/>
+      </c>
+      <c r="K22" s="17">
+        <f>IF((K23&gt;0),K23,(J22*(1+K24)))</f>
+        <v/>
+      </c>
+      <c r="L22" s="17">
+        <f>IF((L23&gt;0),L23,(K22*(1+L24)))</f>
+        <v/>
+      </c>
+      <c r="M22" s="17">
+        <f>IF((M23&gt;0),M23,(L22*(1+M24)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>감가상각비 실적</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>dep_actual</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>35.71458</v>
+      </c>
+      <c r="E23" s="19" t="n">
+        <v>45.83276</v>
+      </c>
+      <c r="F23" s="19" t="n">
+        <v>53.90911</v>
+      </c>
+      <c r="G23" s="19" t="n">
+        <v>59.76686</v>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>75.01629</v>
+      </c>
+      <c r="I23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>감가상각 증가율</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>dep_g</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="25" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J24" s="25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K24" s="25" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L24" s="25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M24" s="25" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
           <t>기타비용</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>other_cost</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>억원</t>
         </is>
       </c>
-      <c r="D14" s="16">
-        <f>IF((D15&gt;0),D15,(D17*D16))</f>
-        <v/>
-      </c>
-      <c r="E14" s="16">
-        <f>IF((E15&gt;0),E15,(E17*E16))</f>
-        <v/>
-      </c>
-      <c r="F14" s="16">
-        <f>IF((F15&gt;0),F15,(F17*F16))</f>
-        <v/>
-      </c>
-      <c r="G14" s="16">
-        <f>IF((G15&gt;0),G15,(G17*G16))</f>
-        <v/>
-      </c>
-      <c r="H14" s="16">
-        <f>IF((H15&gt;0),H15,(H17*H16))</f>
-        <v/>
-      </c>
-      <c r="I14" s="17">
-        <f>IF((I15&gt;0),I15,(I17*I16))</f>
-        <v/>
-      </c>
-      <c r="J14" s="17">
-        <f>IF((J15&gt;0),J15,(J17*J16))</f>
-        <v/>
-      </c>
-      <c r="K14" s="17">
-        <f>IF((K15&gt;0),K15,(K17*K16))</f>
-        <v/>
-      </c>
-      <c r="L14" s="17">
-        <f>IF((L15&gt;0),L15,(L17*L16))</f>
-        <v/>
-      </c>
-      <c r="M14" s="17">
-        <f>IF((M15&gt;0),M15,(M17*M16))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="D25" s="16">
+        <f>IF((D26&gt;0),D26,(D28*D27))</f>
+        <v/>
+      </c>
+      <c r="E25" s="16">
+        <f>IF((E26&gt;0),E26,(E28*E27))</f>
+        <v/>
+      </c>
+      <c r="F25" s="16">
+        <f>IF((F26&gt;0),F26,(F28*F27))</f>
+        <v/>
+      </c>
+      <c r="G25" s="16">
+        <f>IF((G26&gt;0),G26,(G28*G27))</f>
+        <v/>
+      </c>
+      <c r="H25" s="16">
+        <f>IF((H26&gt;0),H26,(H28*H27))</f>
+        <v/>
+      </c>
+      <c r="I25" s="17">
+        <f>IF((I26&gt;0),I26,(I28*I27))</f>
+        <v/>
+      </c>
+      <c r="J25" s="17">
+        <f>IF((J26&gt;0),J26,(J28*J27))</f>
+        <v/>
+      </c>
+      <c r="K25" s="17">
+        <f>IF((K26&gt;0),K26,(K28*K27))</f>
+        <v/>
+      </c>
+      <c r="L25" s="17">
+        <f>IF((L26&gt;0),L26,(L28*L27))</f>
+        <v/>
+      </c>
+      <c r="M25" s="17">
+        <f>IF((M26&gt;0),M26,(M28*M27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>기타비용 실적</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>other_actual</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>억원</t>
         </is>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D26" s="19" t="n">
         <v>1611.4808117</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E26" s="19" t="n">
         <v>1785.00435726</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F26" s="19" t="n">
         <v>1628.70819668</v>
       </c>
-      <c r="G15" s="19" t="n">
+      <c r="G26" s="19" t="n">
         <v>1706.66660828</v>
       </c>
-      <c r="H15" s="19" t="n">
+      <c r="H26" s="19" t="n">
         <v>2250.33474673</v>
       </c>
-      <c r="I15" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="I26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>기타비용률</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>other_ratio</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="26" t="n">
+      <c r="D27" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="25" t="n">
         <v>0.83</v>
       </c>
-      <c r="J16" s="26" t="n">
+      <c r="J27" s="25" t="n">
         <v>0.825</v>
       </c>
-      <c r="K16" s="26" t="n">
+      <c r="K27" s="25" t="n">
         <v>0.82</v>
       </c>
-      <c r="L16" s="26" t="n">
+      <c r="L27" s="25" t="n">
         <v>0.8149999999999999</v>
       </c>
-      <c r="M16" s="26" t="n">
+      <c r="M27" s="25" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>억원</t>
         </is>
       </c>
-      <c r="D17" s="16">
-        <f>(D18*D21)</f>
-        <v/>
-      </c>
-      <c r="E17" s="16">
-        <f>(E18*E21)</f>
-        <v/>
-      </c>
-      <c r="F17" s="16">
-        <f>(F18*F21)</f>
-        <v/>
-      </c>
-      <c r="G17" s="16">
-        <f>(G18*G21)</f>
-        <v/>
-      </c>
-      <c r="H17" s="16">
-        <f>(H18*H21)</f>
-        <v/>
-      </c>
-      <c r="I17" s="17">
-        <f>(I18*I21)</f>
-        <v/>
-      </c>
-      <c r="J17" s="17">
-        <f>(J18*J21)</f>
-        <v/>
-      </c>
-      <c r="K17" s="17">
-        <f>(K18*K21)</f>
-        <v/>
-      </c>
-      <c r="L17" s="17">
-        <f>(L18*L21)</f>
-        <v/>
-      </c>
-      <c r="M17" s="17">
-        <f>(M18*M21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="D28" s="16">
+        <f>(D29*D32)</f>
+        <v/>
+      </c>
+      <c r="E28" s="16">
+        <f>(E29*E32)</f>
+        <v/>
+      </c>
+      <c r="F28" s="16">
+        <f>(F29*F32)</f>
+        <v/>
+      </c>
+      <c r="G28" s="16">
+        <f>(G29*G32)</f>
+        <v/>
+      </c>
+      <c r="H28" s="16">
+        <f>(H29*H32)</f>
+        <v/>
+      </c>
+      <c r="I28" s="17">
+        <f>(I29*I32)</f>
+        <v/>
+      </c>
+      <c r="J28" s="17">
+        <f>(J29*J32)</f>
+        <v/>
+      </c>
+      <c r="K28" s="17">
+        <f>(K29*K32)</f>
+        <v/>
+      </c>
+      <c r="L28" s="17">
+        <f>(L29*L32)</f>
+        <v/>
+      </c>
+      <c r="M28" s="17">
+        <f>(M29*M32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>출하량</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>qty</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>천㎡</t>
         </is>
       </c>
-      <c r="D18" s="16">
-        <f>(D19*D20)</f>
-        <v/>
-      </c>
-      <c r="E18" s="16">
-        <f>(E19*E20)</f>
-        <v/>
-      </c>
-      <c r="F18" s="16">
-        <f>(F19*F20)</f>
-        <v/>
-      </c>
-      <c r="G18" s="16">
-        <f>(G19*G20)</f>
-        <v/>
-      </c>
-      <c r="H18" s="16">
-        <f>(H19*H20)</f>
-        <v/>
-      </c>
-      <c r="I18" s="17">
-        <f>(I19*I20)</f>
-        <v/>
-      </c>
-      <c r="J18" s="17">
-        <f>(J19*J20)</f>
-        <v/>
-      </c>
-      <c r="K18" s="17">
-        <f>(K19*K20)</f>
-        <v/>
-      </c>
-      <c r="L18" s="17">
-        <f>(L19*L20)</f>
-        <v/>
-      </c>
-      <c r="M18" s="17">
-        <f>(M19*M20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="D29" s="16">
+        <f>(D30*D31)</f>
+        <v/>
+      </c>
+      <c r="E29" s="16">
+        <f>(E30*E31)</f>
+        <v/>
+      </c>
+      <c r="F29" s="16">
+        <f>(F30*F31)</f>
+        <v/>
+      </c>
+      <c r="G29" s="16">
+        <f>(G30*G31)</f>
+        <v/>
+      </c>
+      <c r="H29" s="16">
+        <f>(H30*H31)</f>
+        <v/>
+      </c>
+      <c r="I29" s="17">
+        <f>(I30*I31)</f>
+        <v/>
+      </c>
+      <c r="J29" s="17">
+        <f>(J30*J31)</f>
+        <v/>
+      </c>
+      <c r="K29" s="17">
+        <f>(K30*K31)</f>
+        <v/>
+      </c>
+      <c r="L29" s="17">
+        <f>(L30*L31)</f>
+        <v/>
+      </c>
+      <c r="M29" s="17">
+        <f>(M30*M31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>생산능력</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>capacity</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>천㎡</t>
         </is>
       </c>
-      <c r="D19" s="19" t="n">
+      <c r="D30" s="19" t="n">
         <v>342</v>
       </c>
-      <c r="E19" s="19" t="n">
+      <c r="E30" s="19" t="n">
         <v>348</v>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F30" s="19" t="n">
         <v>348</v>
       </c>
-      <c r="G19" s="19" t="n">
+      <c r="G30" s="19" t="n">
         <v>348</v>
       </c>
-      <c r="H19" s="19" t="n">
+      <c r="H30" s="19" t="n">
         <v>348</v>
       </c>
-      <c r="I19" s="20" t="n">
+      <c r="I30" s="20" t="n">
         <v>360</v>
       </c>
-      <c r="J19" s="20" t="n">
+      <c r="J30" s="20" t="n">
         <v>400</v>
       </c>
-      <c r="K19" s="20" t="n">
+      <c r="K30" s="20" t="n">
         <v>430</v>
       </c>
-      <c r="L19" s="20" t="n">
+      <c r="L30" s="20" t="n">
         <v>450</v>
       </c>
-      <c r="M19" s="20" t="n">
+      <c r="M30" s="20" t="n">
         <v>460</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="24" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t>가동률</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>util</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D20" s="25" t="n">
+      <c r="D31" s="24" t="n">
         <v>0.860946317519296</v>
       </c>
-      <c r="E20" s="25" t="n">
+      <c r="E31" s="24" t="n">
         <v>0.8028427797711249</v>
       </c>
-      <c r="F20" s="25" t="n">
+      <c r="F31" s="24" t="n">
         <v>0.6552676032886309</v>
       </c>
-      <c r="G20" s="25" t="n">
+      <c r="G31" s="24" t="n">
         <v>0.613460265575915</v>
       </c>
-      <c r="H20" s="25" t="n">
+      <c r="H31" s="24" t="n">
         <v>0.6780144209429898</v>
       </c>
-      <c r="I20" s="26" t="n">
+      <c r="I31" s="25" t="n">
         <v>0.7</v>
       </c>
-      <c r="J20" s="26" t="n">
+      <c r="J31" s="25" t="n">
         <v>0.72</v>
       </c>
-      <c r="K20" s="26" t="n">
+      <c r="K31" s="25" t="n">
         <v>0.74</v>
       </c>
-      <c r="L20" s="26" t="n">
+      <c r="L31" s="25" t="n">
         <v>0.76</v>
       </c>
-      <c r="M20" s="26" t="n">
+      <c r="M31" s="25" t="n">
         <v>0.78</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="23" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="23" t="inlineStr">
         <is>
           <t>단가</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>억원/천㎡</t>
         </is>
       </c>
-      <c r="D21" s="19" t="n">
+      <c r="D32" s="19" t="n">
         <v>6.04869</v>
       </c>
-      <c r="E21" s="19" t="n">
+      <c r="E32" s="19" t="n">
         <v>7.92973</v>
       </c>
-      <c r="F21" s="19" t="n">
+      <c r="F32" s="19" t="n">
         <v>7.51236</v>
       </c>
-      <c r="G21" s="19" t="n">
+      <c r="G32" s="19" t="n">
         <v>8.4316</v>
       </c>
-      <c r="H21" s="19" t="n">
+      <c r="H32" s="19" t="n">
         <v>10.95566</v>
       </c>
-      <c r="I21" s="20" t="n">
+      <c r="I32" s="20" t="n">
         <v>13.42</v>
       </c>
-      <c r="J21" s="20" t="n">
+      <c r="J32" s="20" t="n">
         <v>14.23</v>
       </c>
-      <c r="K21" s="20" t="n">
+      <c r="K32" s="20" t="n">
         <v>14.66</v>
       </c>
-      <c r="L21" s="20" t="n">
+      <c r="L32" s="20" t="n">
         <v>14.95</v>
       </c>
-      <c r="M21" s="20" t="n">
+      <c r="M32" s="20" t="n">
         <v>15.25</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>순차입금</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>net_debt</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>억원</t>
         </is>
       </c>
-      <c r="D22" s="19" t="n">
+      <c r="D33" s="19" t="n">
         <v>70.03945403</v>
       </c>
-      <c r="E22" s="19" t="n">
+      <c r="E33" s="19" t="n">
         <v>-52.71277978</v>
       </c>
-      <c r="F22" s="19" t="n">
+      <c r="F33" s="19" t="n">
         <v>298.34463868</v>
       </c>
-      <c r="G22" s="19" t="n">
+      <c r="G33" s="19" t="n">
         <v>334.64758095</v>
       </c>
-      <c r="H22" s="19" t="n">
+      <c r="H33" s="19" t="n">
         <v>617.63877813</v>
       </c>
-      <c r="I22" s="20" t="n">
+      <c r="I33" s="20" t="n">
         <v>617.63877813</v>
       </c>
-      <c r="J22" s="20" t="n">
+      <c r="J33" s="20" t="n">
         <v>617.63877813</v>
       </c>
-      <c r="K22" s="20" t="n">
+      <c r="K33" s="20" t="n">
         <v>617.63877813</v>
       </c>
-      <c r="L22" s="20" t="n">
+      <c r="L33" s="20" t="n">
         <v>617.63877813</v>
       </c>
-      <c r="M22" s="20" t="n">
+      <c r="M33" s="20" t="n">
         <v>617.63877813</v>
       </c>
     </row>
@@ -2579,7 +3540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2644,14 +3605,14 @@
       <c r="C5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>ev_value - net_debt</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>'=(I6-I22)</t>
+          <t>'=(I6-I33)</t>
         </is>
       </c>
     </row>
@@ -2669,7 +3630,7 @@
       <c r="C6" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>ebitda * target_ev_ebitda</t>
         </is>
@@ -2694,14 +3655,14 @@
       <c r="C7" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>op_profit + dep_total</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>'=(I9+I11)</t>
+          <t>'=(I9+I22)</t>
         </is>
       </c>
     </row>
@@ -2719,139 +3680,214 @@
       <c r="C8" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>revenue - total_cost</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>'=(I17-I10)</t>
+          <t>'=(I28-I21)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>total_cost</t>
+          <t>net_income</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>총비용</t>
+          <t>지배주주 순이익 (참고)</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D9" s="27" t="inlineStr">
-        <is>
-          <t>dep_total + other_cost</t>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>IF(ni_hist &gt; 0, ni_actual, (op_profit + nonop) * (1 - tax_rate) * ctrl_ratio)</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>'=(I11+I14)</t>
+          <t>'=IF((I11&gt;0),I12,(((I9+I13)*(1-I14))*I15))</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>dep_total</t>
+          <t>eps</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>감가상각비</t>
+          <t>EPS (참고)</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D10" s="27" t="inlineStr">
-        <is>
-          <t>IF(dep_actual &gt; 0, dep_actual, PREV(dep_total) * (1 + dep_g))</t>
+        <v>16</v>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>net_income / shares * 100</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>'=IF((I12&gt;0),I12,(H11*(1+I13)))</t>
+          <t>'=((I10/I17)*100)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>other_cost</t>
+          <t>dps</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>기타비용</t>
+          <t>DPS (참고)</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="D11" s="27" t="inlineStr">
-        <is>
-          <t>IF(other_actual &gt; 0, other_actual, revenue * other_ratio)</t>
+        <v>18</v>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>IF(ni_hist &gt; 0, dps_a, eps * payout)</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>'=IF((I15&gt;0),I15,(I17*I16))</t>
+          <t>'=IF((I11&gt;0),I19,(I16*I20))</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>revenue</t>
+          <t>total_cost</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>매출</t>
+          <t>총비용</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="D12" s="27" t="inlineStr">
-        <is>
-          <t>qty * price</t>
+        <v>21</v>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>dep_total + other_cost</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>'=(I18*I21)</t>
+          <t>'=(I22+I25)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>dep_total</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>IF(dep_actual &gt; 0, dep_actual, PREV(dep_total) * (1 + dep_g))</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>'=IF((I23&gt;0),I23,(H22*(1+I24)))</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>other_cost</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>기타비용</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>IF(other_actual &gt; 0, other_actual, revenue * other_ratio)</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>'=IF((I26&gt;0),I26,(I28*I27))</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D15" s="28" t="inlineStr">
+        <is>
+          <t>qty * price</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>'=(I29*I32)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>qty</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>출하량</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="D13" s="27" t="inlineStr">
+      <c r="C16" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="D16" s="28" t="inlineStr">
         <is>
           <t>capacity * util</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>'=(I19*I20)</t>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>'=(I30*I31)</t>
         </is>
       </c>
     </row>
@@ -2866,7 +3902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2957,7 +3993,7 @@
           <t>ev_value</t>
         </is>
       </c>
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>사업가치 (EV)</t>
         </is>
@@ -2986,7 +4022,7 @@
           <t>target_ev_ebitda</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>목표 EV/EBITDA</t>
         </is>
@@ -3015,7 +4051,7 @@
           <t>ebitda</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
@@ -3044,7 +4080,7 @@
           <t>op_profit</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>영업이익</t>
         </is>
@@ -3070,12 +4106,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>total_cost</t>
-        </is>
-      </c>
-      <c r="B9" s="31" t="inlineStr">
-        <is>
-          <t>총비용</t>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t>지배주주 순이익 (참고)</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -3086,11 +4122,7 @@
           <t>computed</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
         <v>10</v>
       </c>
@@ -3103,12 +4135,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>dep_total</t>
-        </is>
-      </c>
-      <c r="B10" s="32" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
+          <t>ni_hist</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>순이익 실적 마스크</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -3116,32 +4148,28 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>computed</t>
+          <t>input</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
         <v>11</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>억원</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>dep_actual</t>
+          <t>ni_actual</t>
         </is>
       </c>
       <c r="B11" s="33" t="inlineStr">
         <is>
-          <t>감가상각비 실적</t>
+          <t>순이익 실적</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3161,16 +4189,16 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>dep_g</t>
+          <t>nonop</t>
         </is>
       </c>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>감가상각 증가율</t>
+          <t>영업외손익</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3183,19 +4211,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>억원</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>other_cost</t>
-        </is>
-      </c>
-      <c r="B13" s="32" t="inlineStr">
-        <is>
-          <t>기타비용</t>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>실효세율</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3203,7 +4231,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>computed</t>
+          <t>input</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -3212,23 +4240,23 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>억원</t>
+          <t>%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>other_actual</t>
+          <t>ctrl_ratio</t>
         </is>
       </c>
       <c r="B14" s="33" t="inlineStr">
         <is>
-          <t>기타비용 실적</t>
+          <t>지배지분 비율</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3241,27 +4269,27 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>억원</t>
+          <t>%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>other_ratio</t>
+          <t>eps</t>
         </is>
       </c>
       <c r="B15" s="33" t="inlineStr">
         <is>
-          <t>기타비용률</t>
+          <t>EPS (참고)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>computed</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -3270,27 +4298,27 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>원</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>revenue</t>
-        </is>
-      </c>
-      <c r="B16" s="31" t="inlineStr">
-        <is>
-          <t>매출</t>
+          <t>shares</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="inlineStr">
+        <is>
+          <t>상장주식수</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>computed</t>
+          <t>input</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -3299,23 +4327,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>억원</t>
+          <t>백만주</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>qty</t>
-        </is>
-      </c>
-      <c r="B17" s="32" t="inlineStr">
-        <is>
-          <t>출하량</t>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t>DPS (참고)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3328,23 +4356,23 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>천㎡</t>
+          <t>원</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>capacity</t>
-        </is>
-      </c>
-      <c r="B18" s="33" t="inlineStr">
-        <is>
-          <t>생산능력</t>
+          <t>dps_a</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>DPS 실적</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3357,23 +4385,23 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>천㎡</t>
+          <t>원</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>util</t>
-        </is>
-      </c>
-      <c r="B19" s="33" t="inlineStr">
-        <is>
-          <t>가동률</t>
+          <t>payout</t>
+        </is>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>배당성향</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3393,49 +4421,53 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>total_cost</t>
         </is>
       </c>
       <c r="B20" s="32" t="inlineStr">
         <is>
-          <t>단가</t>
+          <t>총비용</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>computed</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="F20" t="n">
         <v>21</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>억원/천㎡</t>
+          <t>억원</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>net_debt</t>
-        </is>
-      </c>
-      <c r="B21" s="28" t="inlineStr">
-        <is>
-          <t>순차입금</t>
+          <t>dep_total</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>computed</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -3443,6 +4475,325 @@
         <v>22</v>
       </c>
       <c r="G21" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>dep_actual</t>
+        </is>
+      </c>
+      <c r="B22" s="34" t="inlineStr">
+        <is>
+          <t>감가상각비 실적</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>23</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>dep_g</t>
+        </is>
+      </c>
+      <c r="B23" s="34" t="inlineStr">
+        <is>
+          <t>감가상각 증가율</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>24</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>other_cost</t>
+        </is>
+      </c>
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>기타비용</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>25</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>other_actual</t>
+        </is>
+      </c>
+      <c r="B25" s="34" t="inlineStr">
+        <is>
+          <t>기타비용 실적</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>6</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>26</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>other_ratio</t>
+        </is>
+      </c>
+      <c r="B26" s="34" t="inlineStr">
+        <is>
+          <t>기타비용률</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>27</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="B27" s="32" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>28</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>qty</t>
+        </is>
+      </c>
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t>출하량</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>29</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>천㎡</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="B29" s="34" t="inlineStr">
+        <is>
+          <t>생산능력</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>30</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>천㎡</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>util</t>
+        </is>
+      </c>
+      <c r="B30" s="34" t="inlineStr">
+        <is>
+          <t>가동률</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>6</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>31</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="B31" s="33" t="inlineStr">
+        <is>
+          <t>단가</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>32</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>억원/천㎡</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>net_debt</t>
+        </is>
+      </c>
+      <c r="B32" s="29" t="inlineStr">
+        <is>
+          <t>순차입금</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>33</v>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>억원</t>
         </is>
@@ -3615,44 +4966,44 @@
           <t>부모 − 자식합</t>
         </is>
       </c>
-      <c r="D5" s="34">
-        <f>ROUND(Model!D10-(Model!D11+Model!D14),6)</f>
-        <v/>
-      </c>
-      <c r="E5" s="34">
-        <f>ROUND(Model!E10-(Model!E11+Model!E14),6)</f>
-        <v/>
-      </c>
-      <c r="F5" s="34">
-        <f>ROUND(Model!F10-(Model!F11+Model!F14),6)</f>
-        <v/>
-      </c>
-      <c r="G5" s="34">
-        <f>ROUND(Model!G10-(Model!G11+Model!G14),6)</f>
-        <v/>
-      </c>
-      <c r="H5" s="34">
-        <f>ROUND(Model!H10-(Model!H11+Model!H14),6)</f>
-        <v/>
-      </c>
-      <c r="I5" s="34">
-        <f>ROUND(Model!I10-(Model!I11+Model!I14),6)</f>
-        <v/>
-      </c>
-      <c r="J5" s="34">
-        <f>ROUND(Model!J10-(Model!J11+Model!J14),6)</f>
-        <v/>
-      </c>
-      <c r="K5" s="34">
-        <f>ROUND(Model!K10-(Model!K11+Model!K14),6)</f>
-        <v/>
-      </c>
-      <c r="L5" s="34">
-        <f>ROUND(Model!L10-(Model!L11+Model!L14),6)</f>
-        <v/>
-      </c>
-      <c r="M5" s="34">
-        <f>ROUND(Model!M10-(Model!M11+Model!M14),6)</f>
+      <c r="D5" s="36">
+        <f>ROUND(Model!D21-(Model!D22+Model!D25),6)</f>
+        <v/>
+      </c>
+      <c r="E5" s="36">
+        <f>ROUND(Model!E21-(Model!E22+Model!E25),6)</f>
+        <v/>
+      </c>
+      <c r="F5" s="36">
+        <f>ROUND(Model!F21-(Model!F22+Model!F25),6)</f>
+        <v/>
+      </c>
+      <c r="G5" s="36">
+        <f>ROUND(Model!G21-(Model!G22+Model!G25),6)</f>
+        <v/>
+      </c>
+      <c r="H5" s="36">
+        <f>ROUND(Model!H21-(Model!H22+Model!H25),6)</f>
+        <v/>
+      </c>
+      <c r="I5" s="36">
+        <f>ROUND(Model!I21-(Model!I22+Model!I25),6)</f>
+        <v/>
+      </c>
+      <c r="J5" s="36">
+        <f>ROUND(Model!J21-(Model!J22+Model!J25),6)</f>
+        <v/>
+      </c>
+      <c r="K5" s="36">
+        <f>ROUND(Model!K21-(Model!K22+Model!K25),6)</f>
+        <v/>
+      </c>
+      <c r="L5" s="36">
+        <f>ROUND(Model!L21-(Model!L22+Model!L25),6)</f>
+        <v/>
+      </c>
+      <c r="M5" s="36">
+        <f>ROUND(Model!M21-(Model!M22+Model!M25),6)</f>
         <v/>
       </c>
     </row>
@@ -3711,7 +5062,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>daa847eeeff1695c</t>
+          <t>822ce4110f600741</t>
         </is>
       </c>
     </row>
@@ -3746,7 +5097,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -3756,7 +5107,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">

--- a/companies/tlb/model.xlsx
+++ b/companies/tlb/model.xlsx
@@ -5062,7 +5062,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>822ce4110f600741</t>
+          <t>5ba005bb2a3cf61b</t>
         </is>
       </c>
     </row>

--- a/companies/tlb/model.xlsx
+++ b/companies/tlb/model.xlsx
@@ -5062,7 +5062,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5ba005bb2a3cf61b</t>
+          <t>034e592f8e6c37b4</t>
         </is>
       </c>
     </row>

--- a/companies/tlb/model.xlsx
+++ b/companies/tlb/model.xlsx
@@ -5062,7 +5062,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>034e592f8e6c37b4</t>
+          <t>3c8dabc616c45d52</t>
         </is>
       </c>
     </row>

--- a/companies/tlb/model.xlsx
+++ b/companies/tlb/model.xlsx
@@ -5062,7 +5062,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3c8dabc616c45d52</t>
+          <t>060f7ff47fb7fba5</t>
         </is>
       </c>
     </row>

--- a/companies/tlb/model.xlsx
+++ b/companies/tlb/model.xlsx
@@ -5062,7 +5062,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>060f7ff47fb7fba5</t>
+          <t>70ec17785f99ddfe</t>
         </is>
       </c>
     </row>

--- a/companies/tlb/model.xlsx
+++ b/companies/tlb/model.xlsx
@@ -5062,7 +5062,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>70ec17785f99ddfe</t>
+          <t>14766e9a7705aec5</t>
         </is>
       </c>
     </row>

--- a/companies/tlb/model.xlsx
+++ b/companies/tlb/model.xlsx
@@ -5062,7 +5062,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14766e9a7705aec5</t>
+          <t>3716f1c0a5dd7c32</t>
         </is>
       </c>
     </row>

--- a/companies/tlb/model.xlsx
+++ b/companies/tlb/model.xlsx
@@ -5062,7 +5062,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3716f1c0a5dd7c32</t>
+          <t>5aa1378b26a70143</t>
         </is>
       </c>
     </row>

--- a/companies/tlb/model.xlsx
+++ b/companies/tlb/model.xlsx
@@ -5062,7 +5062,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5aa1378b26a70143</t>
+          <t>92930dd42f727696</t>
         </is>
       </c>
     </row>

--- a/companies/tlb/model.xlsx
+++ b/companies/tlb/model.xlsx
@@ -5062,7 +5062,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>92930dd42f727696</t>
+          <t>cb1c1c6a77d07fff</t>
         </is>
       </c>
     </row>

--- a/companies/tlb/model.xlsx
+++ b/companies/tlb/model.xlsx
@@ -5062,7 +5062,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>cb1c1c6a77d07fff</t>
+          <t>714d21399cae1d30</t>
         </is>
       </c>
     </row>

--- a/companies/tlb/model.xlsx
+++ b/companies/tlb/model.xlsx
@@ -1728,7 +1728,7 @@
       </c>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>[객관 실적 / 주관 추정] 공시 기준 월 29,000㎡ × 12개월 = 348천㎡로 2022년 이후 **4년째 고정**이다. 이것이 이 모델의 상한선이고, 증설 없이는 물량이 348천㎡를 넘을 수 없다. 추정 구간은 2025년 CAPEX 368.8억(감가상각의 4.9배)을 근거로 늘렸으나 **회사가 증설 계획을 수치로 공시하지 않아 이 부분은 판단이다**. 민감도 뷰에서 영향도를 확인할 것.</t>
+          <t>[객관 실적 / 주관 추정] 공시 기준 월 29,000㎡ × 12개월 = 348천㎡로 2022년 이후 **4년째 고정**이다. 이것이 이 모델의 상한선이고, 증설 없이는 물량이 348천㎡를 넘을 수 없다. 추정 구간은 2025년 CAPEX 368.8억(감가상각의 4.9배)을 근거로 늘려 잡았고, 2026-09 증권사 실사(IBK)로 방향이 확인됐다 — 2Q26 베트남 2공장·안산에 매스램 병목 해소 설비 가동, **베트남 신공장 4Q27 가동 예정**(2027 400천㎡ 가정과 정합). 다만 회사가 수치로 공시한 계획은 여전히 없어 이 부분은 판단이다. 민감도 뷰에서 영향도를 확인할 것.</t>
         </is>
       </c>
     </row>
@@ -1764,23 +1764,23 @@
         <v>0.6780144209429898</v>
       </c>
       <c r="I19" s="13" t="n">
-        <v>0.7</v>
+        <v>0.717</v>
       </c>
       <c r="J19" s="13" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="K19" s="13" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="M19" s="13" t="n">
         <v>0.78</v>
       </c>
       <c r="N19" s="11" t="inlineStr">
         <is>
-          <t>[객관 실적 / 주관 추정] 출하량 ÷ 생산능력. 실적 86.1 → 80.3 → 65.5 → 61.3 → 67.8%. 공시의 가동률(생산실적 기준)과는 재고 변동만큼 다르다. 2026 상반기 실적에서 역산한 연환산 가동률이 69.3%라 2026년을 70.0%로 두고 연 2%p씩 올렸다. **2021년 수준(86.1%) 복귀는 가정하지 않았다** — 그 회복이 이 종목의 가장 큰 상방이고 Bull에서만 반영한다.</t>
+          <t>[주관] 출하량 ÷ 생산능력. 실적 86.1 → 80.3 → 65.5 → 61.3 → 67.8%. 공시의 가동률(생산실적 기준)과는 재고 변동만큼 다르다. 2026 상반기 역산 연환산 69.3%에, 2Q26부터 가동된 매스램(적층 압착) 병목 해소 설비로 하반기 생산 확대(분기 생산면적 6.5 → 7.2만㎡ 추정 — IBK 파악)를 반영해 71.7%로 상향. 이후 연 1~2%p 개선. **2021년 수준(86.1%) 복귀는 여전히 가정하지 않는다** — 그 회복이 가장 큰 상방이고 Bull에서만 반영. 2026-09-04 재보정 — MEMO.revision 참조.</t>
         </is>
       </c>
     </row>
@@ -1816,23 +1816,23 @@
         <v>10.95566</v>
       </c>
       <c r="I20" s="10" t="n">
-        <v>13.42</v>
+        <v>14.15</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>14.23</v>
+        <v>15.57</v>
       </c>
       <c r="K20" s="10" t="n">
-        <v>14.66</v>
+        <v>16.04</v>
       </c>
       <c r="L20" s="10" t="n">
-        <v>14.95</v>
+        <v>16.36</v>
       </c>
       <c r="M20" s="10" t="n">
-        <v>15.25</v>
+        <v>16.69</v>
       </c>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>[객관 실적 / 주관 추정] 공시 "주요제품 가격변동 추이"(원/㎡)를 억원/천㎡로 환산. 실적 604,869 → 792,973 → 751,236 → 843,160 → 1,095,566원/㎡. 2026 상반기 공시값이 **1,361,056원/㎡로 +24.2%** 더 올랐다. 하반기 소폭 조정을 가정해 2026년 연평균을 13.42(=1,342,000원/㎡)로 두고, 이후 +6/+3/+2/+2%로 체감시켰다. 단가 상승은 DDR5·고다층 전환의 결과이므로 전환이 끝나면 멈춘다 — 영구히 오르는 값이 아니다.</t>
+          <t>[주관] 공시 "주요제품 가격변동 추이"(원/㎡)를 억원/천㎡로 환산. 실적 604,869 → 792,973 → 751,236 → 843,160 → 1,095,566원/㎡, 2026 상반기 공시값 **1,361,056원/㎡(+24.2%)**. 초안은 하반기 조정을 가정해 연평균 13.42로 뒀으나, SOCAMM(쏘캠) 양산이 방향을 뒤집었다 — 판가가 일반 서버 기판의 약 3배(IBK 파악)인 쏘캠 비중이 2Q26 11% → 4Q26 26%(추정)로 올라 하반기 blended 단가는 조정이 아니라 상승이 맞다. 2026 연평균 14.15(H1 13.61 확정 + H2 쏘캠 믹스), 2027 +10%(쏘캠 비중 ~30% — 회사 가이던스 1,500억), 이후 +3/+2/+2%로 체감. 2026-09-04 재보정 — MEMO.revision 참조.</t>
         </is>
       </c>
     </row>
@@ -3420,16 +3420,16 @@
         <v>0.6780144209429898</v>
       </c>
       <c r="I31" s="25" t="n">
-        <v>0.7</v>
+        <v>0.717</v>
       </c>
       <c r="J31" s="25" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="K31" s="25" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="L31" s="25" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="M31" s="25" t="n">
         <v>0.78</v>
@@ -3467,19 +3467,19 @@
         <v>10.95566</v>
       </c>
       <c r="I32" s="20" t="n">
-        <v>13.42</v>
+        <v>14.15</v>
       </c>
       <c r="J32" s="20" t="n">
-        <v>14.23</v>
+        <v>15.57</v>
       </c>
       <c r="K32" s="20" t="n">
-        <v>14.66</v>
+        <v>16.04</v>
       </c>
       <c r="L32" s="20" t="n">
-        <v>14.95</v>
+        <v>16.36</v>
       </c>
       <c r="M32" s="20" t="n">
-        <v>15.25</v>
+        <v>16.69</v>
       </c>
     </row>
     <row r="33">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>714d21399cae1d30</t>
+          <t>c5144fadc8a1016e</t>
         </is>
       </c>
     </row>
